--- a/INCIDENCIAS/RITM0054591/ParticipanteData_002001081.xlsx
+++ b/INCIDENCIAS/RITM0054591/ParticipanteData_002001081.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\EXT\21\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://inycom-my.sharepoint.com/personal/a3446_inycom_es/Documents/repositorio/TAREAS/INCIDENCIAS/RITM0054591/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{7E38D6B3-E5A8-4B7D-A550-0AB48D1005EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15" yWindow="-735" windowWidth="28830" windowHeight="15885" tabRatio="763" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="763" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="2" r:id="rId1"/>
@@ -348,7 +348,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -356,16 +356,16 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -375,7 +375,7 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
